--- a/data.mn/public/datasets/cpi-by-category-ulaanbaatar.xlsx
+++ b/data.mn/public/datasets/cpi-by-category-ulaanbaatar.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="CPI by Category" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="English" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Монгол" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -417,17 +418,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>month</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -466,7 +467,7 @@
         <v>2.3</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.2666666666666666</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -488,7 +489,7 @@
         <v>1.666666666666667</v>
       </c>
       <c r="C3" t="n">
-        <v>0.03333333333333333</v>
+        <v>0.0333333333333333</v>
       </c>
       <c r="D3" t="n">
         <v>0.1</v>
@@ -538,7 +539,7 @@
         <v>0.25</v>
       </c>
       <c r="E5" t="n">
-        <v>0.07500000000000001</v>
+        <v>0.075</v>
       </c>
       <c r="F5" t="n">
         <v>-2.7</v>
@@ -554,7 +555,7 @@
         <v>0.6999999999999998</v>
       </c>
       <c r="C6" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.0666666666666666</v>
       </c>
       <c r="D6" t="n">
         <v>0.15</v>
@@ -576,7 +577,7 @@
         <v>0.7999999999999999</v>
       </c>
       <c r="C7" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.0666666666666666</v>
       </c>
       <c r="D7" t="n">
         <v>0.2</v>
@@ -670,7 +671,7 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0.07500000000000001</v>
+        <v>0.075</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -708,13 +709,13 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="D13" t="n">
         <v>-0.45</v>
       </c>
       <c r="E13" t="n">
-        <v>0.07500000000000001</v>
+        <v>0.075</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -752,7 +753,7 @@
         <v>1.533333333333333</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1666666666666666</v>
       </c>
       <c r="D15" t="n">
         <v>0.4</v>
@@ -796,7 +797,7 @@
         <v>1.066666666666667</v>
       </c>
       <c r="C17" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.0666666666666666</v>
       </c>
       <c r="D17" t="n">
         <v>0.25</v>
@@ -840,7 +841,7 @@
         <v>0.3</v>
       </c>
       <c r="C19" t="n">
-        <v>0.03333333333333333</v>
+        <v>0.0333333333333333</v>
       </c>
       <c r="D19" t="n">
         <v>0.15</v>
@@ -859,7 +860,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.3333333333333332</v>
       </c>
       <c r="C20" t="n">
         <v>0.6</v>
@@ -1060,13 +1061,13 @@
         <v>2.233333333333333</v>
       </c>
       <c r="C29" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.2666666666666666</v>
       </c>
       <c r="D29" t="n">
         <v>1.35</v>
       </c>
       <c r="E29" t="n">
-        <v>0.9249999999999999</v>
+        <v>0.925</v>
       </c>
       <c r="F29" t="n">
         <v>0.5</v>
@@ -1176,7 +1177,7 @@
         <v>1.5</v>
       </c>
       <c r="E34" t="n">
-        <v>0.325</v>
+        <v>0.3249999999999999</v>
       </c>
       <c r="F34" t="n">
         <v>0.3</v>
@@ -1220,7 +1221,7 @@
         <v>2.95</v>
       </c>
       <c r="E36" t="n">
-        <v>0.04999999999999999</v>
+        <v>0.0499999999999999</v>
       </c>
       <c r="F36" t="n">
         <v>0.2</v>
@@ -1283,7 +1284,7 @@
         <v>0.7666666666666667</v>
       </c>
       <c r="D39" t="n">
-        <v>0.05000000000000004</v>
+        <v>0.05</v>
       </c>
       <c r="E39" t="n">
         <v>0.25</v>
@@ -1330,7 +1331,7 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>0.225</v>
+        <v>0.2249999999999999</v>
       </c>
       <c r="F41" t="n">
         <v>-0.3</v>
@@ -1343,7 +1344,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.9666666666666667</v>
+        <v>0.9666666666666668</v>
       </c>
       <c r="C42" t="n">
         <v>0.3333333333333333</v>
@@ -1365,10 +1366,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-0.03333333333333336</v>
+        <v>-0.0333333333333333</v>
       </c>
       <c r="C43" t="n">
-        <v>0.03333333333333335</v>
+        <v>0.0333333333333333</v>
       </c>
       <c r="D43" t="n">
         <v>0.75</v>
@@ -1390,7 +1391,7 @@
         <v>-0.5333333333333332</v>
       </c>
       <c r="C44" t="n">
-        <v>0.03333333333333333</v>
+        <v>0.0333333333333333</v>
       </c>
       <c r="D44" t="n">
         <v>1.4</v>
@@ -1409,7 +1410,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.06666666666666665</v>
+        <v>0.0666666666666666</v>
       </c>
       <c r="C45" t="n">
         <v>-0.2333333333333333</v>
@@ -1522,13 +1523,13 @@
         <v>0.7666666666666666</v>
       </c>
       <c r="C50" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1666666666666666</v>
       </c>
       <c r="D50" t="n">
         <v>0.55</v>
       </c>
       <c r="E50" t="n">
-        <v>0.07500000000000001</v>
+        <v>0.075</v>
       </c>
       <c r="F50" t="n">
         <v>-0.5</v>
@@ -1610,7 +1611,7 @@
         <v>0.5333333333333333</v>
       </c>
       <c r="C54" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.2666666666666666</v>
       </c>
       <c r="D54" t="n">
         <v>0.35</v>
@@ -1629,7 +1630,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.2</v>
+        <v>-0.1999999999999999</v>
       </c>
       <c r="C55" t="n">
         <v>0.7333333333333334</v>
@@ -1660,7 +1661,7 @@
         <v>3.25</v>
       </c>
       <c r="E56" t="n">
-        <v>5.774999999999999</v>
+        <v>5.775</v>
       </c>
       <c r="F56" t="n">
         <v>0.8</v>
@@ -1726,7 +1727,7 @@
         <v>0.25</v>
       </c>
       <c r="E59" t="n">
-        <v>0.225</v>
+        <v>0.2249999999999999</v>
       </c>
       <c r="F59" t="n">
         <v>0.9</v>
@@ -1774,6 +1775,1380 @@
       </c>
       <c r="F61" t="n">
         <v>0.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F61"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>сар</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Бусад бараа</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Орон сууц, хэрэгсэл</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Тээвэр</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Хүнс, хоол</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Үйлчилгээ</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2020-02</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.2666666666666666</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2020-03</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.0333333333333333</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.075</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2020-04</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-0.1333333333333333</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.6333333333333333</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2020-05</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.075</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2020-06</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.0666666666666666</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.6999999999999998</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2020-07</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.0666666666666666</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.7999999999999999</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.025</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2020-08</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-1.533333333333333</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2020-09</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.3666666666666667</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-0.8000000000000002</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.275</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2020-10</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.2333333333333333</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2020-11</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.7333333333333334</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.075</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2020-12</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-4.933333333333334</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2021-01</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.3999999999999999</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.075</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2021-02</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2.066666666666667</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2021-03</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.1666666666666666</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1.533333333333333</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.025</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2021-04</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2021-05</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.0666666666666666</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1.066666666666667</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.225</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2021-06</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.325</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2021-07</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.0333333333333333</v>
+      </c>
+      <c r="D19" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2021-08</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-0.3333333333333332</v>
+      </c>
+      <c r="F20" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2021-09</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2021-10</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-2.200000000000001</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2021-11</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.4666666666666666</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2021-12</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1.733333333333333</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2.933333333333334</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2022-01</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1.933333333333334</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.975</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2022-02</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.7666666666666666</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.4666666666666667</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.95</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2022-03</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.4333333333333333</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.4333333333333333</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2022-04</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="C28" t="n">
+        <v>4.433333333333334</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1.366666666666666</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.025</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2022-05</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.2666666666666666</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2.233333333333333</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.925</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2022-06</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.7666666666666666</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2.233333333333333</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2022-07</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.7333333333333334</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.075</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2022-08</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.6000000000000001</v>
+      </c>
+      <c r="D32" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="E32" t="n">
+        <v>-0.8333333333333334</v>
+      </c>
+      <c r="F32" t="n">
+        <v>3.025</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2022-09</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D33" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="E33" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2022-10</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1.033333333333333</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.3249999999999999</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2022-11</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.7666666666666666</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1.033333333333333</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2022-12</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.4000000000000001</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.8666666666666666</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.0499999999999999</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2023-01</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.8999999999999999</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2023-02</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.4666666666666666</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1.433333333333333</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.175</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2023-03</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.7666666666666667</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2023-04</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.2333333333333333</v>
+      </c>
+      <c r="D40" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E40" t="n">
+        <v>2.533333333333333</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2023-05</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D41" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.2249999999999999</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2023-06</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.9666666666666668</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2023-07</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.0333333333333333</v>
+      </c>
+      <c r="D43" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="E43" t="n">
+        <v>-0.0333333333333333</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2023-08</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0.0333333333333333</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E44" t="n">
+        <v>-0.5333333333333332</v>
+      </c>
+      <c r="F44" t="n">
+        <v>5.875</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2023-09</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="C45" t="n">
+        <v>-0.2333333333333333</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.0666666666666666</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2023-10</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2023-11</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="C47" t="n">
+        <v>1.133333333333333</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.025</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2023-12</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.2333333333333333</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2024-01</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.8000000000000002</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2024-02</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0.1666666666666666</v>
+      </c>
+      <c r="D50" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.7666666666666666</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.075</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C51" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2024-05</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.2333333333333333</v>
+      </c>
+      <c r="D53" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2024-06</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0.2666666666666666</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.5333333333333333</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2024-07</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0.7333333333333334</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" t="n">
+        <v>-0.1999999999999999</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.025</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E56" t="n">
+        <v>-0.7666666666666666</v>
+      </c>
+      <c r="F56" t="n">
+        <v>5.775</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0.3666666666666667</v>
+      </c>
+      <c r="D57" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="C58" t="n">
+        <v>1.133333333333334</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.3666666666666667</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.225</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C59" t="n">
+        <v>4.600000000000001</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.2249999999999999</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0.8000000000000002</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="E60" t="n">
+        <v>1.233333333333333</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.025</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="C61" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E61" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F61" t="n">
+        <v>3.85</v>
       </c>
     </row>
   </sheetData>

--- a/data.mn/public/datasets/cpi-by-category-ulaanbaatar.xlsx
+++ b/data.mn/public/datasets/cpi-by-category-ulaanbaatar.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="English" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Монгол" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="English" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Монгол" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -123,6 +123,36 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>data.mn</author>
+  </authors>
+  <commentList>
+    <comment ref="A62" authorId="0" shapeId="0">
+      <text>
+        <t>Basis change: 2020=100 → 2023=100</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>data.mn</author>
+  </authors>
+  <commentList>
+    <comment ref="A62" authorId="0" shapeId="0">
+      <text>
+        <t>Суурь өөрчлөгдсөн: 2020=100 → 2023=100</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -414,14 +444,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:F79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -467,7 +497,7 @@
         <v>2.3</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2666666666666666</v>
+        <v>0.267</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -486,10 +516,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.666666666666667</v>
+        <v>1.667</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0333333333333333</v>
+        <v>0.033</v>
       </c>
       <c r="D3" t="n">
         <v>0.1</v>
@@ -508,10 +538,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.633</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.133</v>
       </c>
       <c r="D4" t="n">
         <v>-0.55</v>
@@ -530,7 +560,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7000000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="C5" t="n">
         <v>0.3</v>
@@ -552,10 +582,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6999999999999998</v>
+        <v>0.7</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0666666666666666</v>
+        <v>0.067</v>
       </c>
       <c r="D6" t="n">
         <v>0.15</v>
@@ -574,10 +604,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7999999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0666666666666666</v>
+        <v>0.067</v>
       </c>
       <c r="D7" t="n">
         <v>0.2</v>
@@ -596,10 +626,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-1.533333333333333</v>
+        <v>-1.533</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.133</v>
       </c>
       <c r="D8" t="n">
         <v>1.05</v>
@@ -618,10 +648,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.8000000000000002</v>
+        <v>-0.8</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3666666666666667</v>
+        <v>0.367</v>
       </c>
       <c r="D9" t="n">
         <v>0.6</v>
@@ -643,7 +673,7 @@
         <v>0.5</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.233</v>
       </c>
       <c r="D10" t="n">
         <v>1.05</v>
@@ -662,10 +692,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7333333333333334</v>
+        <v>0.733</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.333</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -684,10 +714,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.333</v>
       </c>
       <c r="C12" t="n">
-        <v>-4.933333333333334</v>
+        <v>-4.933</v>
       </c>
       <c r="D12" t="n">
         <v>0.5</v>
@@ -706,10 +736,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.667</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3999999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="D13" t="n">
         <v>-0.45</v>
@@ -728,10 +758,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.066666666666667</v>
+        <v>2.067</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.333</v>
       </c>
       <c r="D14" t="n">
         <v>0.1</v>
@@ -750,10 +780,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.533333333333333</v>
+        <v>1.533</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1666666666666666</v>
+        <v>0.167</v>
       </c>
       <c r="D15" t="n">
         <v>0.4</v>
@@ -794,10 +824,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.066666666666667</v>
+        <v>1.067</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0666666666666666</v>
+        <v>0.067</v>
       </c>
       <c r="D17" t="n">
         <v>0.25</v>
@@ -819,7 +849,7 @@
         <v>1.3</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.133</v>
       </c>
       <c r="D18" t="n">
         <v>0.25</v>
@@ -841,7 +871,7 @@
         <v>0.3</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0333333333333333</v>
+        <v>0.033</v>
       </c>
       <c r="D19" t="n">
         <v>0.15</v>
@@ -860,7 +890,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.3333333333333332</v>
+        <v>-0.333</v>
       </c>
       <c r="C20" t="n">
         <v>0.6</v>
@@ -885,7 +915,7 @@
         <v>-0.1</v>
       </c>
       <c r="C21" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.833</v>
       </c>
       <c r="D21" t="n">
         <v>0.75</v>
@@ -904,10 +934,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.666666666666667</v>
+        <v>1.667</v>
       </c>
       <c r="C22" t="n">
-        <v>-2.200000000000001</v>
+        <v>-2.2</v>
       </c>
       <c r="D22" t="n">
         <v>0.65</v>
@@ -926,10 +956,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.333333333333333</v>
+        <v>1.333</v>
       </c>
       <c r="C23" t="n">
-        <v>0.4666666666666666</v>
+        <v>0.467</v>
       </c>
       <c r="D23" t="n">
         <v>0.3</v>
@@ -948,10 +978,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.933333333333334</v>
+        <v>2.933</v>
       </c>
       <c r="C24" t="n">
-        <v>1.733333333333333</v>
+        <v>1.733</v>
       </c>
       <c r="D24" t="n">
         <v>3.4</v>
@@ -970,7 +1000,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.933333333333334</v>
+        <v>1.933</v>
       </c>
       <c r="C25" t="n">
         <v>1.6</v>
@@ -992,10 +1022,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.467</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7666666666666666</v>
+        <v>0.767</v>
       </c>
       <c r="D26" t="n">
         <v>1.9</v>
@@ -1014,10 +1044,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.4333333333333333</v>
+        <v>0.433</v>
       </c>
       <c r="C27" t="n">
-        <v>0.4333333333333333</v>
+        <v>0.433</v>
       </c>
       <c r="D27" t="n">
         <v>0.75</v>
@@ -1036,10 +1066,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.366666666666666</v>
+        <v>1.367</v>
       </c>
       <c r="C28" t="n">
-        <v>4.433333333333334</v>
+        <v>4.433</v>
       </c>
       <c r="D28" t="n">
         <v>1.3</v>
@@ -1058,10 +1088,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.233333333333333</v>
+        <v>2.233</v>
       </c>
       <c r="C29" t="n">
-        <v>0.2666666666666666</v>
+        <v>0.267</v>
       </c>
       <c r="D29" t="n">
         <v>1.35</v>
@@ -1080,10 +1110,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.233333333333333</v>
+        <v>2.233</v>
       </c>
       <c r="C30" t="n">
-        <v>0.7666666666666666</v>
+        <v>0.767</v>
       </c>
       <c r="D30" t="n">
         <v>0.65</v>
@@ -1102,10 +1132,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.333</v>
       </c>
       <c r="C31" t="n">
-        <v>0.7333333333333334</v>
+        <v>0.733</v>
       </c>
       <c r="D31" t="n">
         <v>0.95</v>
@@ -1124,10 +1154,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.8333333333333334</v>
+        <v>-0.833</v>
       </c>
       <c r="C32" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="D32" t="n">
         <v>2.25</v>
@@ -1168,16 +1198,16 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.033333333333333</v>
+        <v>1.033</v>
       </c>
       <c r="C34" t="n">
-        <v>0.7000000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="D34" t="n">
         <v>1.5</v>
       </c>
       <c r="E34" t="n">
-        <v>0.3249999999999999</v>
+        <v>0.325</v>
       </c>
       <c r="F34" t="n">
         <v>0.3</v>
@@ -1190,10 +1220,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.033333333333333</v>
+        <v>1.033</v>
       </c>
       <c r="C35" t="n">
-        <v>0.7666666666666666</v>
+        <v>0.767</v>
       </c>
       <c r="D35" t="n">
         <v>1.5</v>
@@ -1212,16 +1242,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8666666666666666</v>
+        <v>0.867</v>
       </c>
       <c r="C36" t="n">
-        <v>0.4000000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="D36" t="n">
         <v>2.95</v>
       </c>
       <c r="E36" t="n">
-        <v>0.0499999999999999</v>
+        <v>0.05</v>
       </c>
       <c r="F36" t="n">
         <v>0.2</v>
@@ -1234,16 +1264,16 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.666666666666667</v>
+        <v>1.667</v>
       </c>
       <c r="C37" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.667</v>
       </c>
       <c r="D37" t="n">
         <v>1.4</v>
       </c>
       <c r="E37" t="n">
-        <v>0.8999999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="F37" t="n">
         <v>0.4</v>
@@ -1256,10 +1286,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.433333333333333</v>
+        <v>1.433</v>
       </c>
       <c r="C38" t="n">
-        <v>0.4666666666666666</v>
+        <v>0.467</v>
       </c>
       <c r="D38" t="n">
         <v>2.05</v>
@@ -1281,7 +1311,7 @@
         <v>2.7</v>
       </c>
       <c r="C39" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.767</v>
       </c>
       <c r="D39" t="n">
         <v>0.05</v>
@@ -1300,10 +1330,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2.533333333333333</v>
+        <v>2.533</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.233</v>
       </c>
       <c r="D40" t="n">
         <v>1.8</v>
@@ -1322,7 +1352,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1.166666666666667</v>
+        <v>1.167</v>
       </c>
       <c r="C41" t="n">
         <v>0.2</v>
@@ -1331,7 +1361,7 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>0.2249999999999999</v>
+        <v>0.225</v>
       </c>
       <c r="F41" t="n">
         <v>-0.3</v>
@@ -1344,10 +1374,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.9666666666666668</v>
+        <v>0.967</v>
       </c>
       <c r="C42" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.333</v>
       </c>
       <c r="D42" t="n">
         <v>1.35</v>
@@ -1366,10 +1396,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-0.0333333333333333</v>
+        <v>-0.033</v>
       </c>
       <c r="C43" t="n">
-        <v>0.0333333333333333</v>
+        <v>0.033</v>
       </c>
       <c r="D43" t="n">
         <v>0.75</v>
@@ -1388,10 +1418,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-0.5333333333333332</v>
+        <v>-0.533</v>
       </c>
       <c r="C44" t="n">
-        <v>0.0333333333333333</v>
+        <v>0.033</v>
       </c>
       <c r="D44" t="n">
         <v>1.4</v>
@@ -1410,10 +1440,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.0666666666666666</v>
+        <v>0.067</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.233</v>
       </c>
       <c r="D45" t="n">
         <v>1.15</v>
@@ -1432,10 +1462,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.333</v>
       </c>
       <c r="C46" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.333</v>
       </c>
       <c r="D46" t="n">
         <v>0.65</v>
@@ -1457,7 +1487,7 @@
         <v>0.5</v>
       </c>
       <c r="C47" t="n">
-        <v>1.133333333333333</v>
+        <v>1.133</v>
       </c>
       <c r="D47" t="n">
         <v>1.55</v>
@@ -1476,10 +1506,10 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.233</v>
       </c>
       <c r="C48" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.133</v>
       </c>
       <c r="D48" t="n">
         <v>0.25</v>
@@ -1498,7 +1528,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.8000000000000002</v>
+        <v>0.8</v>
       </c>
       <c r="C49" t="n">
         <v>0.6</v>
@@ -1520,10 +1550,10 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.7666666666666666</v>
+        <v>0.767</v>
       </c>
       <c r="C50" t="n">
-        <v>0.1666666666666666</v>
+        <v>0.167</v>
       </c>
       <c r="D50" t="n">
         <v>0.55</v>
@@ -1564,10 +1594,10 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.667</v>
       </c>
       <c r="C52" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.333</v>
       </c>
       <c r="D52" t="n">
         <v>-0.05</v>
@@ -1589,7 +1619,7 @@
         <v>1.6</v>
       </c>
       <c r="C53" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.233</v>
       </c>
       <c r="D53" t="n">
         <v>0.65</v>
@@ -1608,10 +1638,10 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.533</v>
       </c>
       <c r="C54" t="n">
-        <v>0.2666666666666666</v>
+        <v>0.267</v>
       </c>
       <c r="D54" t="n">
         <v>0.35</v>
@@ -1630,10 +1660,10 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.1999999999999999</v>
+        <v>-0.2</v>
       </c>
       <c r="C55" t="n">
-        <v>0.7333333333333334</v>
+        <v>0.733</v>
       </c>
       <c r="D55" t="n">
         <v>0.3</v>
@@ -1652,10 +1682,10 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.7666666666666666</v>
+        <v>-0.767</v>
       </c>
       <c r="C56" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.833</v>
       </c>
       <c r="D56" t="n">
         <v>3.25</v>
@@ -1677,7 +1707,7 @@
         <v>0.9</v>
       </c>
       <c r="C57" t="n">
-        <v>0.3666666666666667</v>
+        <v>0.367</v>
       </c>
       <c r="D57" t="n">
         <v>1.65</v>
@@ -1696,10 +1726,10 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.3666666666666667</v>
+        <v>0.367</v>
       </c>
       <c r="C58" t="n">
-        <v>1.133333333333334</v>
+        <v>1.133</v>
       </c>
       <c r="D58" t="n">
         <v>1.05</v>
@@ -1718,16 +1748,16 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.333</v>
       </c>
       <c r="C59" t="n">
-        <v>4.600000000000001</v>
+        <v>4.6</v>
       </c>
       <c r="D59" t="n">
         <v>0.25</v>
       </c>
       <c r="E59" t="n">
-        <v>0.2249999999999999</v>
+        <v>0.225</v>
       </c>
       <c r="F59" t="n">
         <v>0.9</v>
@@ -1740,10 +1770,10 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1.233333333333333</v>
+        <v>1.233</v>
       </c>
       <c r="C60" t="n">
-        <v>0.8000000000000002</v>
+        <v>0.8</v>
       </c>
       <c r="D60" t="n">
         <v>0.8</v>
@@ -1765,7 +1795,7 @@
         <v>2.6</v>
       </c>
       <c r="C61" t="n">
-        <v>1.166666666666667</v>
+        <v>1.167</v>
       </c>
       <c r="D61" t="n">
         <v>1.15</v>
@@ -1777,8 +1807,405 @@
         <v>0.1</v>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>1.267</v>
+      </c>
+      <c r="C62" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="F62" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F64" t="n">
+        <v>-1.4</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>0.433</v>
+      </c>
+      <c r="C65" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="F65" t="n">
+        <v>-1.4</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="C66" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="F66" t="n">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="C67" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F67" t="n">
+        <v>-1.8</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>1</v>
+      </c>
+      <c r="C68" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="D68" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="F68" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="C69" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="F69" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>0.5669999999999999</v>
+      </c>
+      <c r="C70" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="D70" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="C71" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="D71" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>1.433</v>
+      </c>
+      <c r="C72" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="F72" t="n">
+        <v>-1.7</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C73" t="n">
+        <v>-0.067</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F73" t="n">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C74" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="F74" t="n">
+        <v>-1.9</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>1.067</v>
+      </c>
+      <c r="C75" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F75" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>3.667</v>
+      </c>
+      <c r="C76" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E76" t="n">
+        <v>6.225</v>
+      </c>
+      <c r="F76" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>1.567</v>
+      </c>
+      <c r="C77" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F77" t="n">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>2.567</v>
+      </c>
+      <c r="C78" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C79" t="n">
+        <v>0.5669999999999999</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F79" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -1788,15 +2215,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:F79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1841,7 +2268,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2666666666666666</v>
+        <v>0.267</v>
       </c>
       <c r="D2" t="n">
         <v>1.4</v>
@@ -1863,13 +2290,13 @@
         <v>0.1</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0333333333333333</v>
+        <v>0.033</v>
       </c>
       <c r="D3" t="n">
         <v>1.7</v>
       </c>
       <c r="E3" t="n">
-        <v>1.666666666666667</v>
+        <v>1.667</v>
       </c>
       <c r="F3" t="n">
         <v>0.075</v>
@@ -1885,13 +2312,13 @@
         <v>-0.55</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.1333333333333333</v>
+        <v>-0.133</v>
       </c>
       <c r="D4" t="n">
         <v>-2.5</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.633</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1913,7 +2340,7 @@
         <v>-2.7</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7000000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="F5" t="n">
         <v>0.075</v>
@@ -1929,13 +2356,13 @@
         <v>0.15</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0666666666666666</v>
+        <v>0.067</v>
       </c>
       <c r="D6" t="n">
         <v>-0.1</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6999999999999998</v>
+        <v>0.7</v>
       </c>
       <c r="F6" t="n">
         <v>0.05</v>
@@ -1951,13 +2378,13 @@
         <v>0.2</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0666666666666666</v>
+        <v>0.067</v>
       </c>
       <c r="D7" t="n">
         <v>0.4</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7999999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="F7" t="n">
         <v>0.025</v>
@@ -1973,13 +2400,13 @@
         <v>1.05</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.133</v>
       </c>
       <c r="D8" t="n">
         <v>0.1</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.533333333333333</v>
+        <v>-1.533</v>
       </c>
       <c r="F8" t="n">
         <v>0.4</v>
@@ -1995,13 +2422,13 @@
         <v>0.6</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3666666666666667</v>
+        <v>0.367</v>
       </c>
       <c r="D9" t="n">
         <v>1.5</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8000000000000002</v>
+        <v>-0.8</v>
       </c>
       <c r="F9" t="n">
         <v>0.275</v>
@@ -2017,7 +2444,7 @@
         <v>1.05</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.233</v>
       </c>
       <c r="D10" t="n">
         <v>2.3</v>
@@ -2039,13 +2466,13 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.333</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7333333333333334</v>
+        <v>0.733</v>
       </c>
       <c r="F11" t="n">
         <v>0.075</v>
@@ -2061,13 +2488,13 @@
         <v>0.5</v>
       </c>
       <c r="C12" t="n">
-        <v>-4.933333333333334</v>
+        <v>-4.933</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.333</v>
       </c>
       <c r="F12" t="n">
         <v>0.125</v>
@@ -2083,13 +2510,13 @@
         <v>-0.45</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3999999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.667</v>
       </c>
       <c r="F13" t="n">
         <v>0.075</v>
@@ -2105,13 +2532,13 @@
         <v>0.1</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.333</v>
       </c>
       <c r="D14" t="n">
         <v>0.3</v>
       </c>
       <c r="E14" t="n">
-        <v>2.066666666666667</v>
+        <v>2.067</v>
       </c>
       <c r="F14" t="n">
         <v>0.1</v>
@@ -2127,13 +2554,13 @@
         <v>0.4</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1666666666666666</v>
+        <v>0.167</v>
       </c>
       <c r="D15" t="n">
         <v>0.1</v>
       </c>
       <c r="E15" t="n">
-        <v>1.533333333333333</v>
+        <v>1.533</v>
       </c>
       <c r="F15" t="n">
         <v>0.025</v>
@@ -2171,13 +2598,13 @@
         <v>0.25</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0666666666666666</v>
+        <v>0.067</v>
       </c>
       <c r="D17" t="n">
         <v>1.6</v>
       </c>
       <c r="E17" t="n">
-        <v>1.066666666666667</v>
+        <v>1.067</v>
       </c>
       <c r="F17" t="n">
         <v>0.225</v>
@@ -2193,7 +2620,7 @@
         <v>0.25</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.133</v>
       </c>
       <c r="D18" t="n">
         <v>3</v>
@@ -2215,7 +2642,7 @@
         <v>0.15</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0333333333333333</v>
+        <v>0.033</v>
       </c>
       <c r="D19" t="n">
         <v>6.4</v>
@@ -2243,7 +2670,7 @@
         <v>1.9</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.3333333333333332</v>
+        <v>-0.333</v>
       </c>
       <c r="F20" t="n">
         <v>4.8</v>
@@ -2259,7 +2686,7 @@
         <v>0.75</v>
       </c>
       <c r="C21" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.833</v>
       </c>
       <c r="D21" t="n">
         <v>0.5</v>
@@ -2281,13 +2708,13 @@
         <v>0.65</v>
       </c>
       <c r="C22" t="n">
-        <v>-2.200000000000001</v>
+        <v>-2.2</v>
       </c>
       <c r="D22" t="n">
         <v>0.2</v>
       </c>
       <c r="E22" t="n">
-        <v>1.666666666666667</v>
+        <v>1.667</v>
       </c>
       <c r="F22" t="n">
         <v>0.1</v>
@@ -2303,13 +2730,13 @@
         <v>0.3</v>
       </c>
       <c r="C23" t="n">
-        <v>0.4666666666666666</v>
+        <v>0.467</v>
       </c>
       <c r="D23" t="n">
         <v>1.5</v>
       </c>
       <c r="E23" t="n">
-        <v>1.333333333333333</v>
+        <v>1.333</v>
       </c>
       <c r="F23" t="n">
         <v>0.15</v>
@@ -2325,13 +2752,13 @@
         <v>3.4</v>
       </c>
       <c r="C24" t="n">
-        <v>1.733333333333333</v>
+        <v>1.733</v>
       </c>
       <c r="D24" t="n">
         <v>0.5</v>
       </c>
       <c r="E24" t="n">
-        <v>2.933333333333334</v>
+        <v>2.933</v>
       </c>
       <c r="F24" t="n">
         <v>1.45</v>
@@ -2353,7 +2780,7 @@
         <v>-2</v>
       </c>
       <c r="E25" t="n">
-        <v>1.933333333333334</v>
+        <v>1.933</v>
       </c>
       <c r="F25" t="n">
         <v>1.975</v>
@@ -2369,13 +2796,13 @@
         <v>1.9</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7666666666666666</v>
+        <v>0.767</v>
       </c>
       <c r="D26" t="n">
         <v>0.5</v>
       </c>
       <c r="E26" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.467</v>
       </c>
       <c r="F26" t="n">
         <v>1.95</v>
@@ -2391,13 +2818,13 @@
         <v>0.75</v>
       </c>
       <c r="C27" t="n">
-        <v>0.4333333333333333</v>
+        <v>0.433</v>
       </c>
       <c r="D27" t="n">
         <v>1.7</v>
       </c>
       <c r="E27" t="n">
-        <v>0.4333333333333333</v>
+        <v>0.433</v>
       </c>
       <c r="F27" t="n">
         <v>0.35</v>
@@ -2413,13 +2840,13 @@
         <v>1.3</v>
       </c>
       <c r="C28" t="n">
-        <v>4.433333333333334</v>
+        <v>4.433</v>
       </c>
       <c r="D28" t="n">
         <v>0.7</v>
       </c>
       <c r="E28" t="n">
-        <v>1.366666666666666</v>
+        <v>1.367</v>
       </c>
       <c r="F28" t="n">
         <v>2.025</v>
@@ -2435,13 +2862,13 @@
         <v>1.35</v>
       </c>
       <c r="C29" t="n">
-        <v>0.2666666666666666</v>
+        <v>0.267</v>
       </c>
       <c r="D29" t="n">
         <v>0.5</v>
       </c>
       <c r="E29" t="n">
-        <v>2.233333333333333</v>
+        <v>2.233</v>
       </c>
       <c r="F29" t="n">
         <v>0.925</v>
@@ -2457,13 +2884,13 @@
         <v>0.65</v>
       </c>
       <c r="C30" t="n">
-        <v>0.7666666666666666</v>
+        <v>0.767</v>
       </c>
       <c r="D30" t="n">
         <v>1.3</v>
       </c>
       <c r="E30" t="n">
-        <v>2.233333333333333</v>
+        <v>2.233</v>
       </c>
       <c r="F30" t="n">
         <v>0.125</v>
@@ -2479,13 +2906,13 @@
         <v>0.95</v>
       </c>
       <c r="C31" t="n">
-        <v>0.7333333333333334</v>
+        <v>0.733</v>
       </c>
       <c r="D31" t="n">
         <v>1.2</v>
       </c>
       <c r="E31" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.333</v>
       </c>
       <c r="F31" t="n">
         <v>0.075</v>
@@ -2501,13 +2928,13 @@
         <v>2.25</v>
       </c>
       <c r="C32" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="D32" t="n">
         <v>-0.5</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.8333333333333334</v>
+        <v>-0.833</v>
       </c>
       <c r="F32" t="n">
         <v>3.025</v>
@@ -2545,16 +2972,16 @@
         <v>1.5</v>
       </c>
       <c r="C34" t="n">
-        <v>0.7000000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="D34" t="n">
         <v>0.3</v>
       </c>
       <c r="E34" t="n">
-        <v>1.033333333333333</v>
+        <v>1.033</v>
       </c>
       <c r="F34" t="n">
-        <v>0.3249999999999999</v>
+        <v>0.325</v>
       </c>
     </row>
     <row r="35">
@@ -2567,13 +2994,13 @@
         <v>1.5</v>
       </c>
       <c r="C35" t="n">
-        <v>0.7666666666666666</v>
+        <v>0.767</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>1.033333333333333</v>
+        <v>1.033</v>
       </c>
       <c r="F35" t="n">
         <v>0.375</v>
@@ -2589,16 +3016,16 @@
         <v>2.95</v>
       </c>
       <c r="C36" t="n">
-        <v>0.4000000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="D36" t="n">
         <v>0.2</v>
       </c>
       <c r="E36" t="n">
-        <v>0.8666666666666666</v>
+        <v>0.867</v>
       </c>
       <c r="F36" t="n">
-        <v>0.0499999999999999</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="37">
@@ -2611,16 +3038,16 @@
         <v>1.4</v>
       </c>
       <c r="C37" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.667</v>
       </c>
       <c r="D37" t="n">
         <v>0.4</v>
       </c>
       <c r="E37" t="n">
-        <v>1.666666666666667</v>
+        <v>1.667</v>
       </c>
       <c r="F37" t="n">
-        <v>0.8999999999999999</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="38">
@@ -2633,13 +3060,13 @@
         <v>2.05</v>
       </c>
       <c r="C38" t="n">
-        <v>0.4666666666666666</v>
+        <v>0.467</v>
       </c>
       <c r="D38" t="n">
         <v>0.2</v>
       </c>
       <c r="E38" t="n">
-        <v>1.433333333333333</v>
+        <v>1.433</v>
       </c>
       <c r="F38" t="n">
         <v>0.175</v>
@@ -2655,7 +3082,7 @@
         <v>0.05</v>
       </c>
       <c r="C39" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.767</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
@@ -2677,13 +3104,13 @@
         <v>1.8</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.233</v>
       </c>
       <c r="D40" t="n">
         <v>-0.3</v>
       </c>
       <c r="E40" t="n">
-        <v>2.533333333333333</v>
+        <v>2.533</v>
       </c>
       <c r="F40" t="n">
         <v>0.2</v>
@@ -2705,10 +3132,10 @@
         <v>-0.3</v>
       </c>
       <c r="E41" t="n">
-        <v>1.166666666666667</v>
+        <v>1.167</v>
       </c>
       <c r="F41" t="n">
-        <v>0.2249999999999999</v>
+        <v>0.225</v>
       </c>
     </row>
     <row r="42">
@@ -2721,13 +3148,13 @@
         <v>1.35</v>
       </c>
       <c r="C42" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.333</v>
       </c>
       <c r="D42" t="n">
         <v>0.2</v>
       </c>
       <c r="E42" t="n">
-        <v>0.9666666666666668</v>
+        <v>0.967</v>
       </c>
       <c r="F42" t="n">
         <v>0.15</v>
@@ -2743,13 +3170,13 @@
         <v>0.75</v>
       </c>
       <c r="C43" t="n">
-        <v>0.0333333333333333</v>
+        <v>0.033</v>
       </c>
       <c r="D43" t="n">
         <v>-0.7</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.0333333333333333</v>
+        <v>-0.033</v>
       </c>
       <c r="F43" t="n">
         <v>0.6</v>
@@ -2765,13 +3192,13 @@
         <v>1.4</v>
       </c>
       <c r="C44" t="n">
-        <v>0.0333333333333333</v>
+        <v>0.033</v>
       </c>
       <c r="D44" t="n">
         <v>0.1</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.5333333333333332</v>
+        <v>-0.533</v>
       </c>
       <c r="F44" t="n">
         <v>5.875</v>
@@ -2787,13 +3214,13 @@
         <v>1.15</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.2333333333333333</v>
+        <v>-0.233</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>0.0666666666666666</v>
+        <v>0.067</v>
       </c>
       <c r="F45" t="n">
         <v>0.2</v>
@@ -2809,13 +3236,13 @@
         <v>0.65</v>
       </c>
       <c r="C46" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.333</v>
       </c>
       <c r="D46" t="n">
         <v>0.3</v>
       </c>
       <c r="E46" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.333</v>
       </c>
       <c r="F46" t="n">
         <v>0.125</v>
@@ -2831,7 +3258,7 @@
         <v>1.55</v>
       </c>
       <c r="C47" t="n">
-        <v>1.133333333333333</v>
+        <v>1.133</v>
       </c>
       <c r="D47" t="n">
         <v>0.5</v>
@@ -2853,13 +3280,13 @@
         <v>0.25</v>
       </c>
       <c r="C48" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.133</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.233</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
@@ -2881,7 +3308,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>0.8000000000000002</v>
+        <v>0.8</v>
       </c>
       <c r="F49" t="n">
         <v>0.85</v>
@@ -2897,13 +3324,13 @@
         <v>0.55</v>
       </c>
       <c r="C50" t="n">
-        <v>0.1666666666666666</v>
+        <v>0.167</v>
       </c>
       <c r="D50" t="n">
         <v>-0.5</v>
       </c>
       <c r="E50" t="n">
-        <v>0.7666666666666666</v>
+        <v>0.767</v>
       </c>
       <c r="F50" t="n">
         <v>0.075</v>
@@ -2941,13 +3368,13 @@
         <v>-0.05</v>
       </c>
       <c r="C52" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.333</v>
       </c>
       <c r="D52" t="n">
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.667</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
@@ -2963,7 +3390,7 @@
         <v>0.65</v>
       </c>
       <c r="C53" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.233</v>
       </c>
       <c r="D53" t="n">
         <v>-1.3</v>
@@ -2985,13 +3412,13 @@
         <v>0.35</v>
       </c>
       <c r="C54" t="n">
-        <v>0.2666666666666666</v>
+        <v>0.267</v>
       </c>
       <c r="D54" t="n">
         <v>0.3</v>
       </c>
       <c r="E54" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.533</v>
       </c>
       <c r="F54" t="n">
         <v>0.05</v>
@@ -3007,13 +3434,13 @@
         <v>0.3</v>
       </c>
       <c r="C55" t="n">
-        <v>0.7333333333333334</v>
+        <v>0.733</v>
       </c>
       <c r="D55" t="n">
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.1999999999999999</v>
+        <v>-0.2</v>
       </c>
       <c r="F55" t="n">
         <v>0.025</v>
@@ -3029,13 +3456,13 @@
         <v>3.25</v>
       </c>
       <c r="C56" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.833</v>
       </c>
       <c r="D56" t="n">
         <v>0.8</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.7666666666666666</v>
+        <v>-0.767</v>
       </c>
       <c r="F56" t="n">
         <v>5.775</v>
@@ -3051,7 +3478,7 @@
         <v>1.65</v>
       </c>
       <c r="C57" t="n">
-        <v>0.3666666666666667</v>
+        <v>0.367</v>
       </c>
       <c r="D57" t="n">
         <v>-0.5</v>
@@ -3073,13 +3500,13 @@
         <v>1.05</v>
       </c>
       <c r="C58" t="n">
-        <v>1.133333333333334</v>
+        <v>1.133</v>
       </c>
       <c r="D58" t="n">
         <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>0.3666666666666667</v>
+        <v>0.367</v>
       </c>
       <c r="F58" t="n">
         <v>0.225</v>
@@ -3095,16 +3522,16 @@
         <v>0.25</v>
       </c>
       <c r="C59" t="n">
-        <v>4.600000000000001</v>
+        <v>4.6</v>
       </c>
       <c r="D59" t="n">
         <v>0.9</v>
       </c>
       <c r="E59" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.333</v>
       </c>
       <c r="F59" t="n">
-        <v>0.2249999999999999</v>
+        <v>0.225</v>
       </c>
     </row>
     <row r="60">
@@ -3117,13 +3544,13 @@
         <v>0.8</v>
       </c>
       <c r="C60" t="n">
-        <v>0.8000000000000002</v>
+        <v>0.8</v>
       </c>
       <c r="D60" t="n">
         <v>1.9</v>
       </c>
       <c r="E60" t="n">
-        <v>1.233333333333333</v>
+        <v>1.233</v>
       </c>
       <c r="F60" t="n">
         <v>0.025</v>
@@ -3139,7 +3566,7 @@
         <v>1.15</v>
       </c>
       <c r="C61" t="n">
-        <v>1.166666666666667</v>
+        <v>1.167</v>
       </c>
       <c r="D61" t="n">
         <v>0.1</v>
@@ -3151,7 +3578,404 @@
         <v>3.85</v>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="C62" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E62" t="n">
+        <v>1.267</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.175</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D64" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="E64" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C65" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D65" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.433</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.225</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C66" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D66" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0.275</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C67" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D67" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>1</v>
+      </c>
+      <c r="C68" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="D68" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E68" t="n">
+        <v>1</v>
+      </c>
+      <c r="F68" t="n">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="C69" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D69" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.175</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="C70" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="D70" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.5669999999999999</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="C71" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="D71" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C72" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D72" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="E72" t="n">
+        <v>1.433</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0.175</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C73" t="n">
+        <v>-0.067</v>
+      </c>
+      <c r="D73" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="E73" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C74" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="D74" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="E74" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0.225</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C75" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="D75" t="n">
+        <v>4</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1.067</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C76" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="D76" t="n">
+        <v>4</v>
+      </c>
+      <c r="E76" t="n">
+        <v>3.667</v>
+      </c>
+      <c r="F76" t="n">
+        <v>6.225</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C77" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="D77" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="E77" t="n">
+        <v>1.567</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C78" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E78" t="n">
+        <v>2.567</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C79" t="n">
+        <v>0.5669999999999999</v>
+      </c>
+      <c r="D79" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
--- a/data.mn/public/datasets/cpi-by-category-ulaanbaatar.xlsx
+++ b/data.mn/public/datasets/cpi-by-category-ulaanbaatar.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="English" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Монгол" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="English" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Монгол" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F79"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2203,6 +2203,50 @@
         <v>1.7</v>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="C80" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E80" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="F80" t="n">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>1</v>
+      </c>
+      <c r="C81" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="D81" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="F81" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -2215,7 +2259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F79"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3974,6 +4018,50 @@
         <v>0.45</v>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="C80" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="D80" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="F80" t="n">
+        <v>5.45</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C81" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="D81" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E81" t="n">
+        <v>1</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0.175</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
